--- a/data/xlsx/bmet--ship-safety-and-firefighting.xlsx
+++ b/data/xlsx/bmet--ship-safety-and-firefighting.xlsx
@@ -647,7 +647,9 @@
       <c r="C16" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>8</v>
       </c>
@@ -673,7 +675,9 @@
       <c r="C17" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>8</v>
       </c>
@@ -699,7 +703,9 @@
       <c r="C18" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>8</v>
       </c>
@@ -725,7 +731,9 @@
       <c r="C19" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>8</v>
       </c>
@@ -751,7 +759,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>9</v>
       </c>
@@ -777,7 +787,9 @@
       <c r="C21" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>9</v>
       </c>
@@ -803,7 +815,9 @@
       <c r="C22" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>8</v>
       </c>
@@ -829,7 +843,9 @@
       <c r="C23" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>6</v>
       </c>
@@ -855,7 +871,9 @@
       <c r="C24" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>7</v>
       </c>
@@ -881,7 +899,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>7</v>
       </c>
@@ -907,7 +927,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>10</v>
       </c>
@@ -933,7 +955,9 @@
       <c r="C27" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>9</v>
       </c>
@@ -959,7 +983,9 @@
       <c r="C28" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>6</v>
       </c>
@@ -985,7 +1011,9 @@
       <c r="C29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>9</v>
       </c>
@@ -1011,7 +1039,9 @@
       <c r="C30" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -1037,7 +1067,9 @@
       <c r="C31" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>8</v>
       </c>
@@ -1063,7 +1095,9 @@
       <c r="C32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>6</v>
       </c>
@@ -1089,7 +1123,9 @@
       <c r="C33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>6</v>
       </c>
@@ -1115,7 +1151,9 @@
       <c r="C34" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -1141,7 +1179,9 @@
       <c r="C35" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>7</v>
       </c>
@@ -1167,7 +1207,9 @@
       <c r="C36" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>4</v>
       </c>
@@ -1193,7 +1235,9 @@
       <c r="C37" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>6</v>
       </c>
